--- a/output/땡초장_원가계산서.xlsx
+++ b/output/땡초장_원가계산서.xlsx
@@ -838,7 +838,7 @@
     <row r="22">
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>2. 인건비 (1명)</t>
+          <t>2. 인건비 (2명)</t>
         </is>
       </c>
     </row>
@@ -851,15 +851,20 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
+          <t>인원(명)</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
           <t>총생산량(병)</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="F23" s="2" t="inlineStr">
         <is>
           <t>투입시간(h)</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr">
+      <c r="G23" s="2" t="inlineStr">
         <is>
           <t>병당 인건비(원)</t>
         </is>
@@ -868,20 +873,23 @@
     <row r="24">
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>1명</t>
+          <t>2명</t>
         </is>
       </c>
       <c r="C24" s="6" t="n">
         <v>15000</v>
       </c>
       <c r="D24" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="E24" s="3" t="n">
         <v>640</v>
       </c>
-      <c r="E24" s="3" t="n">
+      <c r="F24" s="3" t="n">
         <v>16</v>
       </c>
-      <c r="F24" s="7">
-        <f>C24*E24/D24</f>
+      <c r="G24" s="7">
+        <f>C24*D24*F24/E24</f>
         <v/>
       </c>
     </row>
@@ -1018,7 +1026,7 @@
         </is>
       </c>
       <c r="C39" s="7">
-        <f>F24</f>
+        <f>G24</f>
         <v/>
       </c>
     </row>
